--- a/sulamericana/datasets_sula/1_classificados_oitavas_sula.xlsx
+++ b/sulamericana/datasets_sula/1_classificados_oitavas_sula.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>jogo</t>
   </si>
@@ -49,7 +49,28 @@
     <t>Jogo 8 (JG8)</t>
   </si>
   <si>
-    <t>EMPATE</t>
+    <t>JUV. KP</t>
+  </si>
+  <si>
+    <t>Máquina Laranjja</t>
+  </si>
+  <si>
+    <t>dasdoresfc</t>
+  </si>
+  <si>
+    <t>JV5 Tricolor Gaúcho</t>
+  </si>
+  <si>
+    <t>FÚRIA LEON</t>
+  </si>
+  <si>
+    <t>AZURRA82</t>
+  </si>
+  <si>
+    <t>Grêmio imortal 37</t>
+  </si>
+  <si>
+    <t>Mau Humor F.C.</t>
   </si>
 </sst>
 </file>
@@ -428,13 +449,19 @@
       <c r="B2" t="s">
         <v>11</v>
       </c>
+      <c r="C2">
+        <v>13951133</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>30267301</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -442,7 +469,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>7017989</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -450,7 +480,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>1747619</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -458,7 +491,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>18344271</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -466,7 +502,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>18346776</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -474,7 +513,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>24468241</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -482,7 +524,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>19033717</v>
       </c>
     </row>
   </sheetData>
